--- a/Summary Sales Review.xlsx
+++ b/Summary Sales Review.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eyad.Suleiman\Desktop\Test fire base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eyad.Suleiman\Desktop\test project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190CC270-969F-473D-A44B-4FAE473A6AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDF5AD2-C881-49C6-A00E-C2677AD801BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3C1EADD6-2761-4C76-BBBA-A3C6B2146568}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="64">
   <si>
     <t>Customer</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>wesam</t>
+  </si>
+  <si>
+    <t>aaaaa</t>
   </si>
 </sst>
 </file>
@@ -1141,31 +1144,31 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5000</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>5500</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K2">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="L2" s="1">
-        <v>1215</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
